--- a/results/auto_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/auto_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -573,9 +573,6 @@
       <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -590,9 +587,6 @@
       <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -607,9 +601,6 @@
       <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="G7" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -624,9 +615,6 @@
       <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -641,9 +629,6 @@
       <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="G9" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -658,9 +643,6 @@
       <c r="D10" t="s">
         <v>35</v>
       </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -674,9 +656,6 @@
       </c>
       <c r="D11" t="s">
         <v>36</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7">

--- a/results/auto_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/auto_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="45">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>info@tac.org.za</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -522,9 +519,6 @@
       <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -539,9 +533,6 @@
       <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -555,9 +546,6 @@
       </c>
       <c r="D4" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7">

--- a/results/auto_Cape_Town_Health_and_Wellness.xlsx
+++ b/results/auto_Cape_Town_Health_and_Wellness.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="46">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>info@tac.org.za</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -519,6 +522,9 @@
       <c r="D2" t="s">
         <v>27</v>
       </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -533,6 +539,9 @@
       <c r="D3" t="s">
         <v>28</v>
       </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -547,6 +556,9 @@
       <c r="D4" t="s">
         <v>29</v>
       </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
@@ -561,6 +573,9 @@
       <c r="D5" t="s">
         <v>30</v>
       </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
@@ -575,6 +590,9 @@
       <c r="D6" t="s">
         <v>31</v>
       </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
@@ -589,6 +607,9 @@
       <c r="D7" t="s">
         <v>32</v>
       </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
@@ -603,6 +624,9 @@
       <c r="D8" t="s">
         <v>33</v>
       </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
@@ -617,6 +641,9 @@
       <c r="D9" t="s">
         <v>34</v>
       </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
@@ -631,6 +658,9 @@
       <c r="D10" t="s">
         <v>35</v>
       </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -645,6 +675,9 @@
       <c r="D11" t="s">
         <v>36</v>
       </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -659,6 +692,9 @@
       <c r="D12" t="s">
         <v>37</v>
       </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
@@ -673,6 +709,9 @@
       <c r="D13" t="s">
         <v>38</v>
       </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
@@ -687,6 +726,9 @@
       <c r="D14" t="s">
         <v>39</v>
       </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
@@ -701,6 +743,9 @@
       <c r="D15" t="s">
         <v>40</v>
       </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
@@ -715,8 +760,11 @@
       <c r="D16" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -729,8 +777,11 @@
       <c r="D17" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -743,8 +794,11 @@
       <c r="D18" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -756,6 +810,9 @@
       </c>
       <c r="D19" t="s">
         <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
